--- a/Методы и средства криптографической защ инф/Лаба 3/Лаба 3.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 3/Лаба 3.xlsx
@@ -1,35 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrcov\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D7E33A9-CE55-4C04-A83A-827CCC554EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156B6C2F-143B-4C8A-AD39-AF45C9C3140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44A0A0C9-2D0B-4A0E-A457-672252A6AD9E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{44A0A0C9-2D0B-4A0E-A457-672252A6AD9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Трисемуса" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -165,7 +157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,9 +239,6 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -259,17 +248,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -605,374 +597,374 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3325DB2-6816-4D0A-BC0C-817363B9626B}">
   <dimension ref="B5:S19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19">
       <c r="B5" t="s">
         <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>0</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <v>1</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="4">
         <v>3</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="4">
         <v>4</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="4">
         <v>5</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="4">
         <v>6</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="4">
         <v>7</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:19">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7">
-        <f>$K7*L$6+L$6-1</f>
+        <f t="shared" ref="L7:S7" si="0">$K7*L$6+L$6-1</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <f>$K7*M$6+M$6-1</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N7">
-        <f>$K7*N$6+N$6-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O7">
-        <f>$K7*O$6+O$6-1</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P7">
-        <f>$K7*P$6+P$6-1</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q7">
-        <f>$K7*Q$6+Q$6-1</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="R7">
-        <f>$K7*R$6+R$6-1</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S7">
-        <f>$K7*S$6+S$6-1</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="2:19">
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="10">
-        <f>$K8*8+L$6-1</f>
+      <c r="L8" s="7">
+        <f t="shared" ref="L8:S10" si="1">$K8*8+L$6-1</f>
         <v>8</v>
       </c>
       <c r="M8">
-        <f>$K8*8+M$6-1</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N8">
-        <f>$K8*8+N$6-1</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="O8">
-        <f>$K8*8+O$6-1</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="P8">
-        <f>$K8*8+P$6-1</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="Q8">
-        <f>$K8*8+Q$6-1</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="R8">
-        <f>$K8*8+R$6-1</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="S8">
-        <f>$K8*8+S$6-1</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:19">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>2</v>
       </c>
       <c r="L9">
-        <f>$K9*8+L$6-1</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="M9">
-        <f>$K9*8+M$6-1</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="N9">
-        <f>$K9*8+N$6-1</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="O9">
-        <f>$K9*8+O$6-1</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="P9">
-        <f>$K9*8+P$6-1</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Q9">
-        <f>$K9*8+Q$6-1</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="R9">
-        <f>$K9*8+R$6-1</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="S9">
-        <f>$K9*8+S$6-1</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="2:19">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>3</v>
       </c>
       <c r="L10">
-        <f>$K10*8+L$6-1</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="M10">
-        <f>$K10*8+M$6-1</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="N10">
-        <f>$K10*8+N$6-1</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="O10" s="10">
-        <f>$K10*8+O$6-1</f>
+      <c r="O10" s="7">
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="P10">
-        <f>$K10*8+P$6-1</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="Q10">
-        <f>$K10*8+Q$6-1</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="R10">
-        <f>$K10*8+R$6-1</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="S10">
-        <f>$K10*8+S$6-1</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="2:19" ht="15" customHeight="1">
+      <c r="B11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="B13" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="14" spans="2:19">
+      <c r="B14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="N14" s="11" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="N14" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+    <row r="18" spans="2:9">
+      <c r="B18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Методы и средства криптографической защ инф/Лаба 3/Лаба 3.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 3/Лаба 3.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrcov\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156B6C2F-143B-4C8A-AD39-AF45C9C3140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A83F62-78BC-475C-AAED-EA0E1E7531C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{44A0A0C9-2D0B-4A0E-A457-672252A6AD9E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Трисемуса" sheetId="1" r:id="rId1"/>
+    <sheet name="Плейфера" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t>Результат:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Открытый текст:</t>
   </si>
@@ -147,10 +144,16 @@
     <t>ЗН АН ИЯ БЫ ВА ЮТ ДВ ОЯ КО ГО РО ДА: ЛИ БО МЫ ЧТ ОН ИБ УД ЬЗ НА ЕМ, ЛИ БО МЫ ЗН АЕ МЪ, ГД ЕН АЙ ТИ СВ ЕД ЕН ИЯ ОБ ЭТ ОМ</t>
   </si>
   <si>
-    <t xml:space="preserve">ДИ ЗИ КЮ ЕШ ГР </t>
-  </si>
-  <si>
-    <t>+- 16</t>
+    <t>ДИ ЗИ КЮ ЕШ ГР ЪЦ РЖ ЧШ ПЧ БТ ПС НЗ: ЦЛ ОШ ЕЯ ОУ ХП ПЛ ФЗ ЫД ИЗ ЖБ, ЦЛ ОШ ЕЯ ДИ ЗГ ГЯ, ЖА ЙЗ НГ ЦА ЩС ЖЗ ЙЗ КЮ ШО ЪХ ЧБ</t>
+  </si>
+  <si>
+    <t>Зашифрованные биграммы:</t>
+  </si>
+  <si>
+    <t>Шифрованный текст:</t>
+  </si>
+  <si>
+    <t>ДИЗИКЮЕШГРЪЦРЖЧШПЧБТПСНЗ: ЦЛОШЕЯОУХППЛФЗЫДИЗЖБ, ЦЛОШЕЯДИЗГГЯ, ЖАЙЗНГЦАЩСЖЗЙЗКЮШОЪХЧБ</t>
   </si>
 </sst>
 </file>
@@ -167,18 +170,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -237,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -251,17 +248,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -596,45 +597,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3325DB2-6816-4D0A-BC0C-817363B9626B}">
-  <dimension ref="B5:S19"/>
+  <dimension ref="B2:U34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="5" spans="2:19">
+    <row r="2" spans="2:21">
+      <c r="U2" s="11"/>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="U3" s="11"/>
+    </row>
+    <row r="4" spans="2:21">
+      <c r="U4" s="11"/>
+    </row>
+    <row r="5" spans="2:21">
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-    </row>
-    <row r="6" spans="2:19">
+        <v>35</v>
+      </c>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="U5" s="11"/>
+    </row>
+    <row r="6" spans="2:21">
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -663,315 +674,401 @@
       <c r="S6" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="2:19">
+      <c r="U6" s="11"/>
+    </row>
+    <row r="7" spans="2:21">
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="11">
         <f t="shared" ref="L7:S7" si="0">$K7*L$6+L$6-1</f>
         <v>0</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="2:19">
+      <c r="U7" s="11"/>
+    </row>
+    <row r="8" spans="2:21">
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="11">
         <f t="shared" ref="L8:S10" si="1">$K8*8+L$6-1</f>
         <v>8</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="11">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="11">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="11">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="2:19">
+      <c r="U8" s="11"/>
+    </row>
+    <row r="9" spans="2:21">
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
         <v>2</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="11">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="11">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="11">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="11">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="11">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="11">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="11">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="11">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="2:19">
+      <c r="U9" s="11"/>
+    </row>
+    <row r="10" spans="2:21">
       <c r="B10" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
         <v>3</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="11">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="11">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="11">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="11">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="11">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="11">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="11">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="2:19" ht="15" customHeight="1">
-      <c r="B11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="2:19">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:19">
+      <c r="U10" s="11"/>
+    </row>
+    <row r="11" spans="2:21" ht="15" customHeight="1">
+      <c r="B11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="U11" s="11"/>
+    </row>
+    <row r="12" spans="2:21">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="U12" s="11"/>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" s="11"/>
+    </row>
+    <row r="14" spans="2:21">
+      <c r="B14" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="2:19">
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="N14" s="7"/>
+      <c r="U14" s="11"/>
+    </row>
+    <row r="15" spans="2:21">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="U15" s="11"/>
+    </row>
+    <row r="16" spans="2:21">
+      <c r="K16" s="10"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="9"/>
+      <c r="U16" s="11"/>
+    </row>
+    <row r="17" spans="2:21">
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="U17" s="11"/>
+    </row>
+    <row r="18" spans="2:21">
+      <c r="B18" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="N14" s="8" t="s">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="U18" s="11"/>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="U19" s="11"/>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="U20" s="11"/>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="2:19">
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="U21" s="11"/>
+    </row>
+    <row r="22" spans="2:21">
+      <c r="B22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="U22" s="11"/>
+    </row>
+    <row r="23" spans="2:21">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="U23" s="11"/>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="U24" s="11"/>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="U25" s="11"/>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="U26" s="11"/>
+    </row>
+    <row r="27" spans="2:21">
+      <c r="U27" s="11"/>
+    </row>
+    <row r="28" spans="2:21">
+      <c r="U28" s="11"/>
+    </row>
+    <row r="29" spans="2:21">
+      <c r="U29" s="11"/>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="U30" s="11"/>
+    </row>
+    <row r="31" spans="2:21">
+      <c r="U31" s="11"/>
+    </row>
+    <row r="32" spans="2:21">
+      <c r="U32" s="11"/>
+    </row>
+    <row r="33" spans="21:21">
+      <c r="U33" s="11"/>
+    </row>
+    <row r="34" spans="21:21">
+      <c r="U34" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="O5:R5"/>
     <mergeCell ref="B11:I12"/>
     <mergeCell ref="B14:I15"/>
     <mergeCell ref="B18:I19"/>
+    <mergeCell ref="B22:I23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
